--- a/artfynd/A 38929-2025 artfynd.xlsx
+++ b/artfynd/A 38929-2025 artfynd.xlsx
@@ -859,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>

--- a/artfynd/A 38929-2025 artfynd.xlsx
+++ b/artfynd/A 38929-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>133851022</v>
       </c>
       <c r="B4" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>133851078</v>
       </c>
       <c r="B5" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>133851058</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>133850726</v>
       </c>
       <c r="B8" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 38929-2025 artfynd.xlsx
+++ b/artfynd/A 38929-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126390899</v>
+        <v>133851078</v>
       </c>
       <c r="B2" t="n">
-        <v>91655</v>
+        <v>83222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4217</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Riprismyrtjärnen, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611474</v>
+        <v>611441</v>
       </c>
       <c r="R2" t="n">
-        <v>7158050</v>
+        <v>7157982</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-68</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +780,7 @@
         <v>126384002</v>
       </c>
       <c r="B3" t="n">
-        <v>91655</v>
+        <v>92333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,41 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133851022</v>
+        <v>126390899</v>
       </c>
       <c r="B4" t="n">
-        <v>91987</v>
+        <v>92333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>4217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Riprismyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611493</v>
+        <v>611474</v>
       </c>
       <c r="R4" t="n">
-        <v>7158071</v>
+        <v>7158050</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,17 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-52</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,44 +984,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133851078</v>
+        <v>133851058</v>
       </c>
       <c r="B5" t="n">
-        <v>83215</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1027,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611441</v>
+        <v>611464</v>
       </c>
       <c r="R5" t="n">
-        <v>7157982</v>
+        <v>7158023</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-68</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-86</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133851058</v>
+        <v>133850726</v>
       </c>
       <c r="B6" t="n">
-        <v>79366</v>
+        <v>83358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1129,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611464</v>
+        <v>611511</v>
       </c>
       <c r="R6" t="n">
-        <v>7158023</v>
+        <v>7157983</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-86</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-97</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,32 +1302,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133850726</v>
+        <v>133850715</v>
       </c>
       <c r="B8" t="n">
-        <v>83351</v>
+        <v>5201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1333,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611511</v>
+        <v>611464</v>
       </c>
       <c r="R8" t="n">
-        <v>7157983</v>
+        <v>7158023</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,7 +1377,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-97</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-107</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,108 +1401,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>133850715</v>
-      </c>
-      <c r="B9" t="n">
-        <v>5201</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>105930</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Semanotus undatus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Skogen, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>611464</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7158023</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-107</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
